--- a/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
+++ b/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B2" t="str">
         <v>AGING TEST PHONE</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B3" t="str">
         <v>AGING TEST PHONE</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-18</v>
       </c>
       <c r="B4" t="str">
         <v>AGING TEST PHONE</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-19</v>
       </c>
       <c r="B5" t="str">
         <v>AGING TEST PHONE</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B6" t="str">
         <v>AGING TEST PHONE</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-29</v>
       </c>
       <c r="B7" t="str">
         <v>AGING TEST SHS PHONE</v>

--- a/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
+++ b/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-31</v>
       </c>
       <c r="B2" t="str">
         <v>AGING TEST PHONE</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-16</v>
       </c>
       <c r="B3" t="str">
         <v>AGING TEST PHONE</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-18</v>
+        <v>2026-06-21</v>
       </c>
       <c r="B4" t="str">
         <v>AGING TEST PHONE</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="B5" t="str">
         <v>AGING TEST PHONE</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-17</v>
       </c>
       <c r="B6" t="str">
         <v>AGING TEST PHONE</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="B7" t="str">
         <v>AGING TEST SHS PHONE</v>

--- a/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
+++ b/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-31</v>
+        <v>2026-08-01</v>
       </c>
       <c r="B2" t="str">
         <v>AGING TEST PHONE</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-17</v>
       </c>
       <c r="B3" t="str">
         <v>AGING TEST PHONE</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-21</v>
+        <v>2026-06-22</v>
       </c>
       <c r="B4" t="str">
         <v>AGING TEST PHONE</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="B5" t="str">
         <v>AGING TEST PHONE</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="B6" t="str">
         <v>AGING TEST PHONE</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="B7" t="str">
         <v>AGING TEST SHS PHONE</v>

--- a/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
+++ b/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-01</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B2" t="str">
         <v>AGING TEST PHONE</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B3" t="str">
         <v>AGING TEST PHONE</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-22</v>
+        <v>2026-06-23</v>
       </c>
       <c r="B4" t="str">
         <v>AGING TEST PHONE</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="B5" t="str">
         <v>AGING TEST PHONE</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="B6" t="str">
         <v>AGING TEST PHONE</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="B7" t="str">
         <v>AGING TEST SHS PHONE</v>

--- a/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
+++ b/e2e-screenshots/stock-aging-panels/fixtures/AGING_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-03</v>
       </c>
       <c r="B2" t="str">
         <v>AGING TEST PHONE</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-19</v>
       </c>
       <c r="B3" t="str">
         <v>AGING TEST PHONE</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-23</v>
+        <v>2026-06-24</v>
       </c>
       <c r="B4" t="str">
         <v>AGING TEST PHONE</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="B5" t="str">
         <v>AGING TEST PHONE</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="B6" t="str">
         <v>AGING TEST PHONE</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="B7" t="str">
         <v>AGING TEST SHS PHONE</v>
